--- a/artfynd/A 12201-2026 artfynd.xlsx
+++ b/artfynd/A 12201-2026 artfynd.xlsx
@@ -1209,32 +1209,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131832231</v>
+        <v>131830835</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>106160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564994</v>
+        <v>564971</v>
       </c>
       <c r="R7" t="n">
-        <v>6428791</v>
+        <v>6428695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,32 +1421,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131830835</v>
+        <v>131832231</v>
       </c>
       <c r="B9" t="n">
-        <v>106160</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564971</v>
+        <v>564994</v>
       </c>
       <c r="R9" t="n">
-        <v>6428695</v>
+        <v>6428791</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131832164</v>
+        <v>131832047</v>
       </c>
       <c r="B10" t="n">
         <v>99038</v>
@@ -1556,7 +1556,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1566,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564998</v>
+        <v>565028</v>
       </c>
       <c r="R10" t="n">
-        <v>6428775</v>
+        <v>6428712</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131832047</v>
+        <v>131832164</v>
       </c>
       <c r="B11" t="n">
         <v>99038</v>
@@ -1658,11 +1662,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565028</v>
+        <v>564998</v>
       </c>
       <c r="R11" t="n">
-        <v>6428712</v>
+        <v>6428775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,46 +1735,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131832066</v>
+        <v>131832084</v>
       </c>
       <c r="B12" t="n">
-        <v>58061</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565015</v>
+        <v>565005</v>
       </c>
       <c r="R12" t="n">
-        <v>6428755</v>
+        <v>6428736</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,17 +1816,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1849,42 +1841,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131832084</v>
+        <v>131832066</v>
       </c>
       <c r="B13" t="n">
-        <v>99038</v>
+        <v>58061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,13 +1888,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565005</v>
+        <v>565015</v>
       </c>
       <c r="R13" t="n">
-        <v>6428736</v>
+        <v>6428755</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,13 +1926,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12201-2026 artfynd.xlsx
+++ b/artfynd/A 12201-2026 artfynd.xlsx
@@ -1315,32 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131831069</v>
+        <v>131832231</v>
       </c>
       <c r="B8" t="n">
-        <v>106160</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564980</v>
+        <v>564994</v>
       </c>
       <c r="R8" t="n">
-        <v>6428711</v>
+        <v>6428791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,32 +1421,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131832231</v>
+        <v>131831069</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>106160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564994</v>
+        <v>564980</v>
       </c>
       <c r="R9" t="n">
-        <v>6428791</v>
+        <v>6428711</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12201-2026 artfynd.xlsx
+++ b/artfynd/A 12201-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131831097</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131832114</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131830688</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131832028</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131831093</v>
       </c>
       <c r="B6" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>131830835</v>
       </c>
       <c r="B7" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131832231</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>131831069</v>
       </c>
       <c r="B9" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131832047</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>131832164</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,42 +1735,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131832084</v>
+        <v>131832066</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>58063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1778,13 +1782,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565005</v>
+        <v>565015</v>
       </c>
       <c r="R12" t="n">
-        <v>6428736</v>
+        <v>6428755</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1816,13 +1820,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1841,46 +1849,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131832066</v>
+        <v>131832084</v>
       </c>
       <c r="B13" t="n">
-        <v>58061</v>
+        <v>99044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1888,13 +1892,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565015</v>
+        <v>565005</v>
       </c>
       <c r="R13" t="n">
-        <v>6428755</v>
+        <v>6428736</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,17 +1930,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>131830980</v>
       </c>
       <c r="B14" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>131832193</v>
       </c>
       <c r="B15" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>131831043</v>
       </c>
       <c r="B16" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 12201-2026 artfynd.xlsx
+++ b/artfynd/A 12201-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131831097</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131832114</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131830688</v>
       </c>
       <c r="B4" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>131832028</v>
       </c>
       <c r="B5" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131831093</v>
       </c>
       <c r="B6" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>131830835</v>
       </c>
       <c r="B7" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>131832231</v>
       </c>
       <c r="B8" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>131831069</v>
       </c>
       <c r="B9" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>131832047</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>131832164</v>
       </c>
       <c r="B11" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,42 +1735,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131832084</v>
+        <v>131832066</v>
       </c>
       <c r="B12" t="n">
-        <v>99095</v>
+        <v>58109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1778,13 +1782,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565005</v>
+        <v>565015</v>
       </c>
       <c r="R12" t="n">
-        <v>6428736</v>
+        <v>6428755</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1816,13 +1820,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1841,46 +1849,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131832066</v>
+        <v>131832084</v>
       </c>
       <c r="B13" t="n">
-        <v>58107</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1888,13 +1892,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565015</v>
+        <v>565005</v>
       </c>
       <c r="R13" t="n">
-        <v>6428755</v>
+        <v>6428736</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,17 +1930,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>131830980</v>
       </c>
       <c r="B14" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>131832193</v>
       </c>
       <c r="B15" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>131831043</v>
       </c>
       <c r="B16" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 12201-2026 artfynd.xlsx
+++ b/artfynd/A 12201-2026 artfynd.xlsx
@@ -1735,46 +1735,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131832066</v>
+        <v>131832084</v>
       </c>
       <c r="B12" t="n">
-        <v>58109</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,13 +1778,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565015</v>
+        <v>565005</v>
       </c>
       <c r="R12" t="n">
-        <v>6428755</v>
+        <v>6428736</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,17 +1816,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1849,42 +1841,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131832084</v>
+        <v>131832066</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>58109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,13 +1888,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565005</v>
+        <v>565015</v>
       </c>
       <c r="R13" t="n">
-        <v>6428736</v>
+        <v>6428755</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,13 +1926,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12201-2026 artfynd.xlsx
+++ b/artfynd/A 12201-2026 artfynd.xlsx
@@ -1735,42 +1735,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131832084</v>
+        <v>131832066</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>58109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1778,13 +1782,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565005</v>
+        <v>565015</v>
       </c>
       <c r="R12" t="n">
-        <v>6428736</v>
+        <v>6428755</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1816,13 +1820,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1841,46 +1849,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131832066</v>
+        <v>131832084</v>
       </c>
       <c r="B13" t="n">
-        <v>58109</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1888,13 +1892,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565015</v>
+        <v>565005</v>
       </c>
       <c r="R13" t="n">
-        <v>6428755</v>
+        <v>6428736</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,17 +1930,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
